--- a/public/templates/SHS_STOCK_TEMPLATE.xlsx
+++ b/public/templates/SHS_STOCK_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -53,7 +53,7 @@
     <t>IPHONE 13 PRO</t>
   </si>
   <si>
-    <t>350100000023757</t>
+    <t/>
   </si>
   <si>
     <t>A</t>
@@ -77,9 +77,6 @@
     <t>Supplier holding — awaiting delivery</t>
   </si>
   <si>
-    <t>350100000031676</t>
-  </si>
-  <si>
     <t>ONU</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>SAMSUNG GALAXY S23</t>
   </si>
   <si>
-    <t>350100000039595</t>
-  </si>
-  <si>
     <t>Brand new</t>
   </si>
   <si>
@@ -113,9 +107,6 @@
     <t>IPHONE 14</t>
   </si>
   <si>
-    <t>350100000047514</t>
-  </si>
-  <si>
     <t>PURPLE</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>Every row here is Stock Type = SHS. Units land as INCOMING and show under the SHS tile, never on the office shelf.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>LIFECYCLE — an SHS unit leaves SHS in exactly three ways:</t>
   </si>
   <si>
@@ -155,10 +143,16 @@
     <t xml:space="preserve">  3. The supplier cancels → an admin deletes it from the SHS overlay.</t>
   </si>
   <si>
-    <t>IMEI is required here, same as any stock row. If the supplier has not given you IMEIs yet,</t>
-  </si>
-  <si>
-    <t>do not invent them — wait, or record the holding at model level through the master file.</t>
+    <t>LEAVE IMEI BLANK. Supplier-held stock has not shipped — there is no handset in anyone's</t>
+  </si>
+  <si>
+    <t>hand, so there is no IMEI to read off it. That is the whole point of recording it as SHS.</t>
+  </si>
+  <si>
+    <t>The IMEI is captured when the unit arrives and you Receive it. Never invent one: an</t>
+  </si>
+  <si>
+    <t>invented IMEI matches no real phone and has to be found and corrected later.</t>
   </si>
   <si>
     <t>The grey example rows are illustrations — delete them before uploading your own data.</t>
@@ -194,10 +188,13 @@
     <t>Keep spelling consistent with the catalog — model names are decided in Admin → Configuration and applied automatically on import.</t>
   </si>
   <si>
-    <t>15 digits, or a 10-12 char Apple serial</t>
-  </si>
-  <si>
-    <t>The unique key. Required even for SHS: without it the sale that eventually fulfils this unit cannot match it.</t>
+    <t>No — leave blank</t>
+  </si>
+  <si>
+    <t>Blank. (A real IMEI is accepted if the supplier has already sent one.)</t>
+  </si>
+  <si>
+    <t>SHS stock has not shipped, so there is no IMEI yet. The unit is tracked by Model + Supplier until it arrives; if the supplier ships it straight to a customer, the Sales Report fulfils it on that same Model + Supplier match. The IMEI is captured on Receive.</t>
   </si>
   <si>
     <t>A, B, C, ONU, Brand new</t>
@@ -762,19 +759,19 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>18</v>
@@ -794,25 +791,25 @@
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="I4" s="8">
         <v>430</v>
@@ -826,13 +823,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
@@ -844,10 +841,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I5" s="8">
         <v>480</v>
@@ -856,7 +853,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="4:10" x14ac:dyDescent="0.25"/>
@@ -1386,7 +1383,7 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1397,240 +1394,250 @@
   <sheetData>
     <row r="1" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>57</v>
+        <v>5</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>57</v>
+        <v>6</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>73</v>
+      <c r="B30" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
